--- a/data/science_print_answers.xlsx
+++ b/data/science_print_answers.xlsx
@@ -11,6 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-06_B" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-07_A" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-07_B" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-08_A" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-08_B" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-12_A" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-12_B" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,10 +461,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1107,10 +1111,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1617,10 +1621,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2267,10 +2271,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2777,4 +2781,2336 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>section_title</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>q_label</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>answer_yomi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>茎のつくり</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>茎のつくり</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>道管</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>どうかん</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>茎のつくり</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>師管</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>しかん</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>茎のつくり</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>維管束</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>いかんそく</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>茎のつくり</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>茎と葉のつくり</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(1)茎</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>茎と葉のつくり</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>(1)葉</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>エ</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>茎と葉のつくり</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(2)①</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>根</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>茎と葉のつくり</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>(2)②</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>葉</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>は</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>茎と葉のつくり</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>(3)①</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>双子葉類</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>そうしようるい</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>茎と葉のつくり</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>(3)②</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>例）維管束が輪のように並んでいるから</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>茎と葉のつくり</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>さいぼう</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>葉緑体</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>ようりょくたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>(4)①</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>気孔</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>きこう</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>(4)②</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>孔辺細胞</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>こうへんさいぼう</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>昼</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>ひる</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>水蒸気（気体）</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>すいじょうき</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>葉の内部の観察</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>(7)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>蒸散</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>じょうさん</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>section_title</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>q_label</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>answer_yomi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>(1)A</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>呼吸</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>こきゅう</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>(1)B</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>光合成</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>こうごうせい</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>(1)C</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>蒸散</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>じょうさん</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>(2)①</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>葉緑体</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>ようりょくたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>(2)②</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>デンプン</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(2)③</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>みず</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>(2)④</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>師管</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>しかん</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>二酸化炭素</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>にさんかたんそ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>植物の体のつくりとはたらき</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ヒマワリの種子</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>根毛</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>こんもう</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>ヒマワリの種子</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>例）根と土がふれる面積が大きくなるから</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（ワセリン実験）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>例）水面からの水の蒸発を防ぐため</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（ワセリン実験）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>(2)①</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>3.7g</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（ワセリン実験）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>(2)②</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>5.0g</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（ワセリン実験）</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>(2)③</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.2g</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（ワセリン実験）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>8.9g</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2章 植物の体のつくりとはたらき(2)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（ワセリン実験）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>例）気孔は葉の表側よりも裏側のほうが多い</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>section_title</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>q_label</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>answer_yomi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>圧力</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>あつりょく</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>(2)①</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>ニュートン毎平方メートル</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>(2)②</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>パスカル</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>(3)①</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>大きさ</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>おおきさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>(3)②</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>面積</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>めんせき</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>5N</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>(5)①</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0.0025m²</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(5)②</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>2000Pa</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>面に加わる力</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>大きくなる</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>おおきくなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>大気による力</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>(1)①</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>大気圧（気圧）</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>たいきあつ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>大気による力</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>(1)②</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>hPa</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>大気による力</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>海面</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>かいめん</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>大気による力</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>大気による力</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>例）ふくらむ</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>気象要素の観測</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>雲量</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>うんりょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>気象要素の観測</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>晴れ</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>はれ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>気象要素の観測</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>(3)①</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>気象要素の観測</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>(3)②</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>北西</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>ほくせい</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>気象要素の観測</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>(4)①</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>16.0℃</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>気象要素の観測</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>(4)②</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>unit_title</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>section_title</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>q_label</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>answer_yomi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>くもりや雨</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>くもりやあめ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>(2)①</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>イ</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>(2)②</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>ウ</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>1日目</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>いちにちめ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>(4)A</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>気圧</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>きあつ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(4)B</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>湿度</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>しつど</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>(4)C</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>気温</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>きおん</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>気温・湿度・気圧の記録</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>（天気図記号：晴れ・北の風・風力2）</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>スキー板</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>はいているとき</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>スキー板</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>例）スキー板をはくと力がはたらく面積が大きくなり、圧力が小さくなるから</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（直方体の圧力）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>(1)①</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>25N</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（直方体の圧力）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>(1)②</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0.02m²</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（直方体の圧力）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>(1)③</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>1250Pa</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（直方体の圧力）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（直方体の圧力）</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>大気（空気）</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>たいき</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（直方体の圧力）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>ウ</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1章 地球をとり巻く大気のようす</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>入試トレーニング（直方体の圧力）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>X＞Y</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>